--- a/data/trans_dic/IP31KM01_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM01_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,49%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>89,83; 99,09</t>
+          <t>85,29; 97,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>84,15; 97,29</t>
+          <t>89,95; 98,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89,23; 97,11</t>
+          <t>90,33; 97,3</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,75%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>86,38; 94,3</t>
+          <t>87,65; 95,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>88,13; 95,1</t>
+          <t>87,18; 94,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89,05; 94,13</t>
+          <t>89,14; 93,93</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,79%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>86,78; 94,52</t>
+          <t>85,47; 93,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,8; 94,16</t>
+          <t>86,49; 94,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>87,89; 93,38</t>
+          <t>87,57; 93,21</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,53%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>86,75; 93,61</t>
+          <t>83,7; 91,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>79,88; 90,6</t>
+          <t>85,24; 92,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84,64; 91,25</t>
+          <t>85,49; 90,74</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,29%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>88,95; 92,91</t>
+          <t>87,51; 91,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>86,8; 91,59</t>
+          <t>88,58; 92,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88,57; 91,71</t>
+          <t>88,84; 91,77</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>79</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>44595</t>
+          <t>34698</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41872</t>
+          <t>41002</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86466</t>
+          <t>75700</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>41767; 46070</t>
+          <t>31929; 36509</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>38106; 44060</t>
+          <t>38391; 42237</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81894; 89126</t>
+          <t>72371; 77954</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>237</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>145408</t>
+          <t>144536</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>167936</t>
+          <t>133057</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>313345</t>
+          <t>277592</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>137601; 150221</t>
+          <t>137641; 149435</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>160364; 173042</t>
+          <t>126864; 137484</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>303900; 321217</t>
+          <t>269705; 284207</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>213</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>157901</t>
+          <t>181390</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>192894</t>
+          <t>158893</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>350796</t>
+          <t>340283</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>150186; 163584</t>
+          <t>171050; 188063</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>182313; 200072</t>
+          <t>151081; 164492</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>338856; 360033</t>
+          <t>328225; 349347</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>302</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>247944</t>
+          <t>256941</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>264623</t>
+          <t>227821</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>512567</t>
+          <t>484763</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>237940; 256736</t>
+          <t>244604; 266712</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>243632; 276334</t>
+          <t>217641; 235199</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>490295; 528570</t>
+          <t>468105; 496863</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>853</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>831</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>853</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>595849</t>
+          <t>617565</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>667324</t>
+          <t>560772</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1263174</t>
+          <t>1178336</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>580984; 606819</t>
+          <t>601064; 631556</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>646433; 682126</t>
+          <t>547624; 572223</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1238024; 1281985</t>
+          <t>1159390; 1197619</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM01_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM01_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que toman una fruta o un zumo natural todos los días (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>92,69%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>96,07%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>94,49%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>85,29; 97,53</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>89,95; 98,96</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>90,33; 97,3</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>92,04%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>91,44%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>91,75%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>87,65; 95,16</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>87,18; 94,48</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>89,14; 93,93</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>90,64%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>90,97%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>90,79%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>85,47; 93,97</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>86,49; 94,17</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>87,57; 93,21</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>87,93%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>89,22%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>88,53%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>83,7; 91,27</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>85,24; 92,11</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>85,49; 90,74</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>89,92%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>90,71%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>90,29%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>87,51; 91,95</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>88,58; 92,56</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>88,84; 91,77</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.9268823343650037</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.9606609405982438</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.9448774686968814</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>34698</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>41002</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>75700</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.8529140104370309</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.8994856467778232</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.9033307849386035</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>31929; 36509</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>38391; 42237</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>72371; 77954</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.9752698816426222</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.9896065210548607</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.973010695652226</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>491</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.9203628675313449</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.9143652105815538</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.91747826322669</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>144536</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>133057</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>277592</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.8764597224537565</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.8718080431184781</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.8914101932516638</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>137641; 149435</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>126864; 137484</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>269705; 284207</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.9515593740371069</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.9447884624765635</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.9393402244459015</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>436</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.9063794407152017</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.9096622395690588</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.9079093682773937</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>181390</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>158893</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>340283</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.8547133540447689</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.8649395770217709</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.8757371974914424</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>171050; 188063</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>151081; 164492</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>328225; 349347</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.9397208867287857</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.9417221917168463</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.9320953782950813</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.8792706830275235</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.8922373746042087</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.8853173085597953</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>256941</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>227821</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>484763</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.8370499629495819</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.8523681322133627</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.8548965027252112</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>244604; 266712</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>217641; 235199</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>468105; 496863</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.9127051690687972</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.9211311015196095</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.9074168663476535</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>853</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>831</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1684</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.8991603690392778</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.9070932139624025</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.9029182447506929</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>617565</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>560772</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1178336</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.8751361066392803</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.8858254007329041</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.8884007327942175</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>601064; 631556</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>547624; 572223</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1159390; 1197619</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.91953108098611</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.9256149765172565</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.9176935597628771</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que toman una fruta o un zumo natural todos los días (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>34698</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>41002</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>75700</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>31929</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>38391</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>72371</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>36509</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>42237</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>77954</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>254</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>237</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>144536</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>133057</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>277592</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>137641</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>126864</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>269705</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>149435</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>137484</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>284207</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>223</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>213</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>181390</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>158893</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>340283</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>171050</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>151081</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>328225</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>188063</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>164492</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>349347</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>301</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>302</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>256941</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>227821</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>484763</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>244604</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>217641</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>468105</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>266712</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>235199</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>496863</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>853</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>831</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>617565</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>560772</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1178336</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>601064</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>547624</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>1159390</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>631556</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>572223</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>1197619</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>